--- a/food_beverage_order_forms/041_medical_worker_meal_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/041_medical_worker_meal_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>medical Worker meal Order Form</t>
+          <t>What is your meal preference for lunch?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>food preference</t>
+          <t>What is your meal preference for dinner?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>food preference options</t>
+          <t>Do you have any food allergies or dietary restrictions?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>date of birth</t>
+          <t>Do you have any special requests for your meal?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,24 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date of birth</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD</t>
-        </is>
-      </c>
+          <t>What is your contact information?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>meal order</t>
+          <t>Do you have a preferred time for your meal delivery?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,59 +663,59 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>meal order</t>
+          <t>Would you like to add any additional contact information?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>special_request</t>
+          <t>medical_worker_meal_order_form_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>special request</t>
+          <t>Do you want to order a snack?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>special_request</t>
+          <t>medical_worker_meal_order_form_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>special request options</t>
+          <t>Is there a specific date for your meal order?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,25 +727,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>medical_worker_meal_order_form_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact information</t>
+          <t>Do you have any further requests or comments?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,174 +755,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>meal order</t>
+          <t>Do you need any further assistance with your meal order?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>meal_order</t>
+          <t>medical_worker_meal_order_form_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>meal order</t>
+          <t>Do you have any other comments or feedback?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>contact information</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>medical worker contact information</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>meal order</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>medical worker contact information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>contact information</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>contact information</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -941,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -969,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_2_choices</t>
+          <t>medical_worker_meal_order_form_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -986,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_2_choices</t>
+          <t>medical_worker_meal_order_form_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1003,221 +861,170 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_3_choices</t>
+          <t>medical_worker_meal_order_form_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_3_choices</t>
+          <t>medical_worker_meal_order_form_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_3_choices</t>
+          <t>medical_worker_meal_order_form_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_6_choices</t>
+          <t>medical_worker_meal_order_form_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_6_choices</t>
+          <t>medical_worker_meal_order_form_page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_6_choices</t>
+          <t>medical_worker_meal_order_form_page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_7_choices</t>
+          <t>medical_worker_meal_order_form_page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_worker_meal_order_form_page_7_choices</t>
+          <t>medical_worker_meal_order_form_page_8_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>special_request_choices</t>
+          <t>medical_worker_meal_order_form_page_8_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>special_request_choices</t>
+          <t>medical_worker_meal_order_form_page_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medical_worker_meal_order_form_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
